--- a/Examples.xlsx
+++ b/Examples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/Draw_my_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E481DE9-3200-604D-8784-241B8AF246D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E729A00-C02E-1942-9637-2D1C5204DB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="780" windowWidth="39700" windowHeight="25800" activeTab="4" xr2:uid="{A549E01A-21D3-B048-ACE5-6C86109A1619}"/>
+    <workbookView xWindow="9880" yWindow="620" windowWidth="39700" windowHeight="25800" activeTab="3" xr2:uid="{A549E01A-21D3-B048-ACE5-6C86109A1619}"/>
   </bookViews>
   <sheets>
     <sheet name="Example_1" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Example_3" sheetId="8" r:id="rId3"/>
     <sheet name="Example_4" sheetId="6" r:id="rId4"/>
     <sheet name="Example_5" sheetId="7" r:id="rId5"/>
+    <sheet name="Example_6" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>154 lx</t>
   </si>
@@ -1004,7 +1005,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D3" s="3">
-        <v>1000</v>
+        <v>641</v>
       </c>
       <c r="E3" s="6">
         <v>259</v>
@@ -1021,7 +1022,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D4" s="3">
-        <v>900</v>
+        <v>549</v>
       </c>
       <c r="E4" s="3">
         <v>204</v>
@@ -1038,7 +1039,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D5" s="3">
-        <v>700</v>
+        <v>435</v>
       </c>
       <c r="E5" s="3">
         <v>97</v>
@@ -1197,7 +1198,91 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B70E8A-65E2-BF4A-816A-388C2A7529A7}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D3" s="6">
+        <v>735</v>
+      </c>
+      <c r="E3" s="6">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="D4" s="3">
+        <v>52</v>
+      </c>
+      <c r="E4" s="3">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410" xsi:nil="true"/>
@@ -1208,7 +1293,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010038F54DA96D8FE34FA9146A9AF4B710CF" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="efe46b9af7ab9aa636540b7b6da2ef89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2f12b5a-3239-485c-afa7-8bfa8665860f" xmlns:ns3="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f025e5f50a3b2db88aeb3f5b64b9c99" ns2:_="" ns3:_="">
     <xsd:import namespace="f2f12b5a-3239-485c-afa7-8bfa8665860f"/>
@@ -1409,16 +1494,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A32B19E-66BB-48BF-8400-E4A784426B82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A27E043-F4E1-471F-980E-39AA631A596B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -1435,7 +1519,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC9D885-520F-4A97-A487-D90AAF1D146E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1452,12 +1536,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A32B19E-66BB-48BF-8400-E4A784426B82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Examples.xlsx
+++ b/Examples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/Draw_my_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E729A00-C02E-1942-9637-2D1C5204DB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE308E9-F5EC-E042-883A-E41CC3A725B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="620" windowWidth="39700" windowHeight="25800" activeTab="3" xr2:uid="{A549E01A-21D3-B048-ACE5-6C86109A1619}"/>
+    <workbookView xWindow="1420" yWindow="780" windowWidth="39700" windowHeight="25800" activeTab="6" xr2:uid="{A549E01A-21D3-B048-ACE5-6C86109A1619}"/>
   </bookViews>
   <sheets>
     <sheet name="Example_1" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Example_4" sheetId="6" r:id="rId4"/>
     <sheet name="Example_5" sheetId="7" r:id="rId5"/>
     <sheet name="Example_6" sheetId="9" r:id="rId6"/>
+    <sheet name="Example_7" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="21">
   <si>
     <t>154 lx</t>
   </si>
@@ -80,6 +81,30 @@
   </si>
   <si>
     <t>Melanopic EDI (lx)</t>
+  </si>
+  <si>
+    <t>554 lx</t>
+  </si>
+  <si>
+    <t>425 lx</t>
+  </si>
+  <si>
+    <t>496 lx</t>
+  </si>
+  <si>
+    <t>325 lx</t>
+  </si>
+  <si>
+    <t>245 lx</t>
+  </si>
+  <si>
+    <t>100 lx</t>
+  </si>
+  <si>
+    <t>164 lx</t>
+  </si>
+  <si>
+    <t>55 lx</t>
   </si>
 </sst>
 </file>
@@ -1273,27 +1298,116 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA98B8C-02BF-A14D-8205-82CA74C651AB}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2f12b5a-3239-485c-afa7-8bfa8665860f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010038F54DA96D8FE34FA9146A9AF4B710CF" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="efe46b9af7ab9aa636540b7b6da2ef89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2f12b5a-3239-485c-afa7-8bfa8665860f" xmlns:ns3="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f025e5f50a3b2db88aeb3f5b64b9c99" ns2:_="" ns3:_="">
     <xsd:import namespace="f2f12b5a-3239-485c-afa7-8bfa8665860f"/>
@@ -1494,10 +1608,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2f12b5a-3239-485c-afa7-8bfa8665860f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A32B19E-66BB-48BF-8400-E4A784426B82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC9D885-520F-4A97-A487-D90AAF1D146E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f2f12b5a-3239-485c-afa7-8bfa8665860f"/>
+    <ds:schemaRef ds:uri="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1520,20 +1665,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC9D885-520F-4A97-A487-D90AAF1D146E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A32B19E-66BB-48BF-8400-E4A784426B82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f2f12b5a-3239-485c-afa7-8bfa8665860f"/>
-    <ds:schemaRef ds:uri="e7f6b4e8-9e4f-40ca-b4d8-5afb38350410"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>